--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5520-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5520-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73CF54BD-8BC2-47D3-BA73-59A78EB72809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60160403-45B3-4B33-8E63-DC20B27AB912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{13557A7D-B436-4911-A36B-9697E6995693}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E3317A5E-A448-44E4-8710-9BCE9FC162C7}"/>
   </bookViews>
   <sheets>
     <sheet name="5520-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1400,18 +1400,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B95161-DA05-4A4D-9AED-CA20972690A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C25D6109-B4AF-4384-99F7-27C18C5E2FDD}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="2" width="16.375" customWidth="1"/>
+    <col min="3" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1439,7 +1439,7 @@
       <c r="Q1" s="27"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1469,7 +1469,7 @@
       <c r="Q2" s="29"/>
       <c r="R2" s="30"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1565,7 +1565,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="34">
         <v>2025</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <v>2024</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="34">
         <v>2023</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <v>2022</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="34">
         <v>2021</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>2020</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="34">
         <v>2019</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>2018</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="34">
         <v>2017</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>2016</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="34">
         <v>2015</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>2014</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>8.84</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="34">
         <v>2013</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>6.08</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>2012</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="34">
         <v>2011</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>2010</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="34">
         <v>2009</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="36">
         <v>2008</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="34">
         <v>2007</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
         <v>2006</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="34">
         <v>2005</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>7.83</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
         <v>2004</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="34">
         <v>2003</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="36">
         <v>2002</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="34">
         <v>2001</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <v>2000</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="34">
         <v>1999</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="36">
         <v>1998</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
         <v>25</v>
       </c>
